--- a/docs/Generation.xlsx
+++ b/docs/Generation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/EnergyPricingForecast/Recursos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/EnergyPricingForecast/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="90" documentId="11_F25DC773A252ABDACC1048DC8198614A5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{690DD185-FACC-410A-BD2E-781B678BE214}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="1830" windowWidth="16410" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1620" yWindow="2520" windowWidth="16410" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
-    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="20" r:id="rId4"/>
+    <pivotCache cacheId="21" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -559,31 +559,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
@@ -5862,7 +5838,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7631AB2D-104C-4205-B34A-9D5DB27B5923}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7631AB2D-104C-4205-B34A-9D5DB27B5923}" name="PivotTable1" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -5983,24 +5959,24 @@
     <dataField name="Sum of Generación [GWh]" fld="1" baseField="2" baseItem="1" numFmtId="4"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="11">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -6017,7 +5993,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3ADD379C-FA80-4066-B9E9-58945F98C251}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" mergeItem="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3ADD379C-FA80-4066-B9E9-58945F98C251}" name="PivotTable2" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" mergeItem="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="G3:O8" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
@@ -6267,24 +6243,24 @@
     <dataField name="BRIDGE" fld="3" baseField="0" baseItem="0" numFmtId="4"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="15">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
